--- a/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
+++ b/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
+++ b/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>EL CASTILLO DE LA GRAN FAMILIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-15.84749</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.01739000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-15.84749</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.01739</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>193 CLUB DE LEONES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-15.84361</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.02827000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>265</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-15.84361</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.02827</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-15.838498</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.032551</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1914</v>
-      </c>
-      <c r="J4" t="n">
-        <v>136</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-15.838498</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.032551</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>254 / 70045</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-15.855837</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.007227</v>
-      </c>
-      <c r="I5" t="n">
-        <v>226</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-15.855837</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.007227</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>255</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-15.856057</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.01239700000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>234</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-15.856057</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.012397</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-15.831365</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.02768399999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>610</v>
-      </c>
-      <c r="J7" t="n">
-        <v>45</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-15.831365</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.027684</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>296</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-15.883757</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-69.972323</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-15.883757</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-69.972323</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>326 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-15.84347</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.02109</v>
-      </c>
-      <c r="I9" t="n">
-        <v>222</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-15.84347</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.02109</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>70001</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-15.839781</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.031459</v>
-      </c>
-      <c r="I10" t="n">
-        <v>518</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-15.839781</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.031459</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>70003 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-15.84083</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.021202</v>
-      </c>
-      <c r="I11" t="n">
-        <v>630</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-15.84083</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.021202</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>70005 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-15.841065</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.026032</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1008</v>
-      </c>
-      <c r="J12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-15.841065</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.026032</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>GRAN UNIDAD ESCOLAR SAN CARLOS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-15.840344</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.02443</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3136</v>
-      </c>
-      <c r="J13" t="n">
-        <v>187</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-15.840344</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.02443</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>70024</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-15.845818</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.01849</v>
-      </c>
-      <c r="I14" t="n">
-        <v>570</v>
-      </c>
-      <c r="J14" t="n">
-        <v>33</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-15.845818</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.01849</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>70035</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-15.829512</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.01950100000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>524</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-15.829512</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.019501</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>POLITECNICO HUASCAR</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-15.82696</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.03236</v>
-      </c>
-      <c r="I16" t="n">
-        <v>259</v>
-      </c>
-      <c r="J16" t="n">
-        <v>33</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-15.82696</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.03236</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>70623</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-15.853321</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.017613</v>
-      </c>
-      <c r="I17" t="n">
-        <v>312</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-15.853321</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.017613</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>VILLA DEL LAGO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-15.859773</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.01450800000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>347</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-15.859773</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.014508</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>71001 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-15.839062</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.02389700000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1025</v>
-      </c>
-      <c r="J19" t="n">
-        <v>49</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-15.839062</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.023897</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-15.83523</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.023572</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1246</v>
-      </c>
-      <c r="J20" t="n">
-        <v>57</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-15.83523</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.023572</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-15.842175</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.026634</v>
-      </c>
-      <c r="I21" t="n">
-        <v>230</v>
-      </c>
-      <c r="J21" t="n">
-        <v>17</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-15.842175</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-70.026634</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-15.837603</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-70.02723899999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1153</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-15.837603</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-70.027239</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-15.883963</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-70.00161300000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>257</v>
-      </c>
-      <c r="J23" t="n">
-        <v>45</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-15.883963</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-70.001613</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-15.841331</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-70.02985</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1002</v>
-      </c>
-      <c r="J24" t="n">
-        <v>75</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-15.841331</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-70.02985</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>32</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-15.847185</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-70.017189</v>
-      </c>
-      <c r="I25" t="n">
-        <v>607</v>
-      </c>
-      <c r="J25" t="n">
-        <v>62</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-15.847185</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-70.017189</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>45 EMILIO ROMERO PADILLA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-15.841397</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-70.025192</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1029</v>
-      </c>
-      <c r="J26" t="n">
-        <v>60</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-15.841397</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-70.025192</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>CARLOS RUBINA BURGOS</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-15.839708</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-70.02917100000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>412</v>
-      </c>
-      <c r="J27" t="n">
-        <v>29</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-15.839708</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-70.029171</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>JOSE CARLOS MARIATEGUI APLICACION UNA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-15.82745</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-70.017037</v>
-      </c>
-      <c r="I28" t="n">
-        <v>376</v>
-      </c>
-      <c r="J28" t="n">
-        <v>23</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-15.82745</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-70.017037</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>332 / 70808</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-15.875515</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-69.99553899999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>210</v>
-      </c>
-      <c r="J29" t="n">
-        <v>15</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-15.875515</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-69.995539</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-15.841857</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-70.023737</v>
-      </c>
-      <c r="I30" t="n">
-        <v>813</v>
-      </c>
-      <c r="J30" t="n">
-        <v>45</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-15.841857</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-70.023737</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-15.837837</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-70.024328</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1195</v>
-      </c>
-      <c r="J31" t="n">
-        <v>46</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-15.837837</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-70.024328</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>IMAGINA SCHOOL</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-15.848653</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-70.01846999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>255</v>
-      </c>
-      <c r="J32" t="n">
-        <v>25</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-15.848653</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-70.01847</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>ADVENTISTA PUNO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-15.83649</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-70.02933</v>
-      </c>
-      <c r="I33" t="n">
-        <v>558</v>
-      </c>
-      <c r="J33" t="n">
-        <v>32</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-15.83649</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-70.02933</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-15.840065</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-70.029819</v>
-      </c>
-      <c r="I34" t="n">
-        <v>790</v>
-      </c>
-      <c r="J34" t="n">
-        <v>39</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-15.840065</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-70.029819</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>VILLA DE FATIMA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-15.836178</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-70.02925399999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>347</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-15.836178</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-70.029254</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>70078</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-15.97552</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-69.79665</v>
-      </c>
-      <c r="I36" t="n">
-        <v>203</v>
-      </c>
-      <c r="J36" t="n">
-        <v>16</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-15.97552</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-69.79665</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>70695</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-16.501567</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-70.12844699999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-16.501567</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-70.128447</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>MAÑAZO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-15.800255</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-70.35386699999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>245</v>
-      </c>
-      <c r="J38" t="n">
-        <v>31</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-15.800255</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-70.353867</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>EL RECREO ESCOLAR</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-15.86184</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-70.01254</v>
-      </c>
-      <c r="I39" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-15.86184</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-70.01254</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>CLAUDIO GALENO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-15.836925</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-70.027213</v>
-      </c>
-      <c r="I40" t="n">
-        <v>888</v>
-      </c>
-      <c r="J40" t="n">
-        <v>44</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-15.836925</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-70.027213</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>1286</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-15.65363</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-69.84538000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-15.65363</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-69.84538</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>197</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-15.82886</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-70.02987400000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>223</v>
-      </c>
-      <c r="J42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-15.82886</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-70.029874</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-15.865781</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-70.011017</v>
-      </c>
-      <c r="I43" t="n">
-        <v>557</v>
-      </c>
-      <c r="J43" t="n">
-        <v>20</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-15.865781</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-70.011017</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>COLVER</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-15.841445</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-70.025615</v>
-      </c>
-      <c r="I44" t="n">
-        <v>504</v>
-      </c>
-      <c r="J44" t="n">
-        <v>24</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-15.841445</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-70.025615</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>YACHAY SCHOOL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-15.8298</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-70.01779999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>495</v>
-      </c>
-      <c r="J45" t="n">
-        <v>18</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-15.8298</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-70.0178</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>70025 INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-15.83136</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-70.02768</v>
-      </c>
-      <c r="I46" t="n">
-        <v>385</v>
-      </c>
-      <c r="J46" t="n">
-        <v>30</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-15.83136</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-70.02768</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>CRAMER</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-15.85586</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-70.01533000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>515</v>
-      </c>
-      <c r="J47" t="n">
-        <v>27</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-15.85586</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-70.01533</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>INTERNACIONAL WILLIAM HARVEY</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-15.83805</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-70.02556</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-15.83805</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-70.02556</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>JAMES BALDWIN</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-15.845125</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-70.02361500000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>578</v>
-      </c>
-      <c r="J49" t="n">
-        <v>40</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-15.845125</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-70.023615</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
+++ b/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>904428</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EL CASTILLO DE LA GRAN FAMILIA</t>
+          <t>INTERNACIONAL WILLIAM HARVEY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-15.84749</t>
+          <t>-15.83805</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.01739</t>
+          <t>-70.02556</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>440928</t>
+          <t>441206</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>193 CLUB DE LEONES</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.84361</t>
+          <t>-15.883757</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.02827</t>
+          <t>-69.972323</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>440933</t>
+          <t>686067</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.838498</t>
+          <t>-15.65363</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.032551</t>
+          <t>-69.84538</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>441046</t>
+          <t>784138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>254 / 70045</t>
+          <t>197</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.855837</t>
+          <t>-15.82886</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.007227</t>
+          <t>-70.029874</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>441051</t>
+          <t>440928</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>193 CLUB DE LEONES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.856057</t>
+          <t>-15.84361</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.012397</t>
+          <t>-70.02827</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>441089</t>
+          <t>441051</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA NACIONAL</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.831365</t>
+          <t>-15.856057</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.027684</t>
+          <t>-70.012397</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>441206</t>
+          <t>440933</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.883757</t>
+          <t>-15.838498</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-69.972323</t>
+          <t>-70.032551</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>441287</t>
+          <t>441777</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70001</t>
+          <t>332 / 70808</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.839781</t>
+          <t>-15.875515</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.031459</t>
+          <t>-69.995539</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>441292</t>
+          <t>442164</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70003 SAGRADO CORAZON DE JESUS</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.84083</t>
+          <t>-15.97552</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.021202</t>
+          <t>-69.79665</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>441305</t>
+          <t>441635</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70005 CORAZON DE JESUS</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.841065</t>
+          <t>-15.842175</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.026032</t>
+          <t>-70.026634</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>441310</t>
+          <t>441046</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GRAN UNIDAD ESCOLAR SAN CARLOS</t>
+          <t>254 / 70045</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.840344</t>
+          <t>-15.855837</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.02443</t>
+          <t>-70.007227</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>441348</t>
+          <t>833940</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>YACHAY SCHOOL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.845818</t>
+          <t>-15.8298</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.01849</t>
+          <t>-70.0178</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>441367</t>
+          <t>441310</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>GRAN UNIDAD ESCOLAR SAN CARLOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.829512</t>
+          <t>-15.840344</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.019501</t>
+          <t>-70.02443</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>441386</t>
+          <t>442649</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>POLITECNICO HUASCAR</t>
+          <t>70695</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.82696</t>
+          <t>-16.501567</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.03236</t>
+          <t>-70.128447</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>441522</t>
+          <t>538072</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70623</t>
+          <t>EL RECREO ESCOLAR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.853321</t>
+          <t>-15.86184</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.017613</t>
+          <t>-70.01254</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,22 +1493,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>441560</t>
+          <t>441895</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VILLA DEL LAGO</t>
+          <t>VILLA DE FATIMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.859773</t>
+          <t>-15.836178</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.014508</t>
+          <t>-70.029254</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>441616</t>
+          <t>811537</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71001 ALMIRANTE MIGUEL GRAU</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.839062</t>
+          <t>-15.865781</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.023897</t>
+          <t>-70.011017</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>557</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>441621</t>
+          <t>441715</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GLORIOSO SAN CARLOS</t>
+          <t>JOSE CARLOS MARIATEGUI APLICACION UNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.83523</t>
+          <t>-15.82745</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.023572</t>
+          <t>-70.017037</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>441635</t>
+          <t>825011</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>COLVER</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.842175</t>
+          <t>-15.841445</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.026634</t>
+          <t>-70.025615</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>441857</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GLORIOSO SAN CARLOS</t>
+          <t>IMAGINA SCHOOL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.837603</t>
+          <t>-15.848653</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.027239</t>
+          <t>-70.01847</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>441659</t>
+          <t>441287</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-15.883963</t>
+          <t>-15.839781</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.001613</t>
+          <t>-70.031459</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>518</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>441664</t>
+          <t>441522</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>70623</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-15.841331</t>
+          <t>-15.853321</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-70.02985</t>
+          <t>-70.017613</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>441678</t>
+          <t>856026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>CRAMER</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-15.847185</t>
+          <t>-15.85586</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.017189</t>
+          <t>-70.01533</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>441683</t>
+          <t>441697</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>45 EMILIO ROMERO PADILLA</t>
+          <t>CARLOS RUBINA BURGOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.841397</t>
+          <t>-15.839708</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.025192</t>
+          <t>-70.029171</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>441697</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CARLOS RUBINA BURGOS</t>
+          <t>EL CASTILLO DE LA GRAN FAMILIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-15.839708</t>
+          <t>-15.84749</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.029171</t>
+          <t>-70.01739</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>441715</t>
+          <t>855753</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI APLICACION UNA</t>
+          <t>70025 INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-15.82745</t>
+          <t>-15.83136</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.017037</t>
+          <t>-70.02768</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>385</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>441777</t>
+          <t>444035</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>332 / 70808</t>
+          <t>MAÑAZO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-15.875515</t>
+          <t>-15.800255</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-69.995539</t>
+          <t>-70.353867</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>441819</t>
+          <t>441367</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-15.841857</t>
+          <t>-15.829512</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.023737</t>
+          <t>-70.019501</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>441824</t>
+          <t>441862</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>ADVENTISTA PUNO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-15.837837</t>
+          <t>-15.83649</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.024328</t>
+          <t>-70.02933</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>558</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>441857</t>
+          <t>441348</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IMAGINA SCHOOL</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-15.848653</t>
+          <t>-15.845818</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.01847</t>
+          <t>-70.01849</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>570</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>441862</t>
+          <t>441386</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADVENTISTA PUNO</t>
+          <t>POLITECNICO HUASCAR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-15.83649</t>
+          <t>-15.82696</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.02933</t>
+          <t>-70.03236</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>441876</t>
+          <t>441292</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>70003 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-15.840065</t>
+          <t>-15.84083</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.029819</t>
+          <t>-70.021202</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>630</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>441895</t>
+          <t>441560</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VILLA DE FATIMA</t>
+          <t>VILLA DEL LAGO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-15.836178</t>
+          <t>-15.859773</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.029254</t>
+          <t>-70.014508</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>442164</t>
+          <t>441876</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-15.97552</t>
+          <t>-15.840065</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-69.79665</t>
+          <t>-70.029819</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>442649</t>
+          <t>907634</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70695</t>
+          <t>JAMES BALDWIN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.501567</t>
+          <t>-15.845125</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.128447</t>
+          <t>-70.023615</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>444035</t>
+          <t>577803</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MAÑAZO</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-15.800255</t>
+          <t>-15.836925</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.353867</t>
+          <t>-70.027213</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>888</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>538072</t>
+          <t>441089</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EL RECREO ESCOLAR</t>
+          <t>INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-15.86184</t>
+          <t>-15.831365</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.01254</t>
+          <t>-70.027684</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>610</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>577803</t>
+          <t>441659</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-15.836925</t>
+          <t>-15.883963</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.027213</t>
+          <t>-70.001613</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>686067</t>
+          <t>441819</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-15.65363</t>
+          <t>-15.841857</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-69.84538</t>
+          <t>-70.023737</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>813</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>784138</t>
+          <t>441305</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>70005 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-15.82886</t>
+          <t>-15.841065</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.029874</t>
+          <t>-70.026032</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>811537</t>
+          <t>441824</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-15.865781</t>
+          <t>-15.837837</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.011017</t>
+          <t>-70.024328</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>825011</t>
+          <t>441616</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>COLVER</t>
+          <t>71001 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-15.841445</t>
+          <t>-15.839062</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.025615</t>
+          <t>-70.023897</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>833940</t>
+          <t>441621</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>YACHAY SCHOOL</t>
+          <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-15.8298</t>
+          <t>-15.83523</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.0178</t>
+          <t>-70.023572</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>855753</t>
+          <t>441683</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70025 INDEPENDENCIA NACIONAL</t>
+          <t>45 EMILIO ROMERO PADILLA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-15.83136</t>
+          <t>-15.841397</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.02768</t>
+          <t>-70.025192</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>856026</t>
+          <t>441678</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CRAMER</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-15.85586</t>
+          <t>-15.847185</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.01533</t>
+          <t>-70.017189</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>607</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>904428</t>
+          <t>441664</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INTERNACIONAL WILLIAM HARVEY</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-15.83805</t>
+          <t>-15.841331</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.02556</t>
+          <t>-70.02985</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>907634</t>
+          <t>441640</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JAMES BALDWIN</t>
+          <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-15.845125</t>
+          <t>-15.837603</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.023615</t>
+          <t>-70.027239</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
+++ b/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>904428</t>
+          <t>907634</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INTERNACIONAL WILLIAM HARVEY</t>
+          <t>JAMES BALDWIN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-15.83805</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.02556</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.845125</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-70.023615</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>441206</t>
+          <t>904428</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>INTERNACIONAL WILLIAM HARVEY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.883757</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-69.972323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-15.83805</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-70.02556</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>686067</t>
+          <t>856026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>CRAMER</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.65363</t>
+          <t>515</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-69.84538</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-15.85586</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-70.01533</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>784138</t>
+          <t>855753</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>70025 INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.82886</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.029874</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-15.83136</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-70.02768</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>440928</t>
+          <t>833940</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>193 CLUB DE LEONES</t>
+          <t>YACHAY SCHOOL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.84361</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.02827</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-15.8298</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-70.0178</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>441051</t>
+          <t>825011</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>COLVER</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.856057</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.012397</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-15.841445</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-70.025615</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>440933</t>
+          <t>811537</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.838498</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.032551</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>-15.865781</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>-70.011017</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>441249</t>
+          <t>784138</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>326 MANUEL NUÑEZ BUTRON</t>
+          <t>197</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-15.84347</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.02109</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-15.82886</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.029874</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>441777</t>
+          <t>686067</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>332 / 70808</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.875515</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-69.995539</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-15.65363</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-69.84538</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>442164</t>
+          <t>577803</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.97552</t>
+          <t>888</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-69.79665</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-15.836925</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.027213</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>441635</t>
+          <t>538072</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>EL RECREO ESCOLAR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.842175</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.026634</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-15.86184</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-70.01254</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>441046</t>
+          <t>444035</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>254 / 70045</t>
+          <t>MAÑAZO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.855837</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.007227</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-15.800255</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.353867</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>833940</t>
+          <t>442649</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>YACHAY SCHOOL</t>
+          <t>70695</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.8298</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.0178</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-16.501567</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.128447</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>441310</t>
+          <t>442164</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GRAN UNIDAD ESCOLAR SAN CARLOS</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.840344</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.02443</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>-15.97552</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-69.79665</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>442649</t>
+          <t>441895</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70695</t>
+          <t>VILLA DE FATIMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.501567</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.128447</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-15.836178</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-70.029254</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>538072</t>
+          <t>441876</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EL RECREO ESCOLAR</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.86184</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.01254</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-15.840065</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-70.029819</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>441895</t>
+          <t>441862</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VILLA DE FATIMA</t>
+          <t>ADVENTISTA PUNO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.836178</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.029254</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-15.83649</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.02933</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>811537</t>
+          <t>441857</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>IMAGINA SCHOOL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.865781</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.011017</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>-15.848653</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.01847</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>441715</t>
+          <t>441824</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI APLICACION UNA</t>
+          <t>NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.82745</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.017037</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-15.837837</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-70.024328</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>825011</t>
+          <t>441819</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COLVER</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.841445</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.025615</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-15.841857</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.023737</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>441857</t>
+          <t>441777</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IMAGINA SCHOOL</t>
+          <t>332 / 70808</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.848653</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.01847</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-15.875515</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-69.995539</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>441287</t>
+          <t>441715</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70001</t>
+          <t>JOSE CARLOS MARIATEGUI APLICACION UNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-15.839781</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.031459</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>-15.82745</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.017037</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>441522</t>
+          <t>441697</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70623</t>
+          <t>CARLOS RUBINA BURGOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-15.853321</t>
+          <t>412</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-70.017613</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-15.839708</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.029171</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>856026</t>
+          <t>441683</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CRAMER</t>
+          <t>45 EMILIO ROMERO PADILLA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-15.85586</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.01533</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>-15.841397</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-70.025192</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>441697</t>
+          <t>441678</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CARLOS RUBINA BURGOS</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.839708</t>
+          <t>607</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.029171</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>-15.847185</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.017189</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>441664</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EL CASTILLO DE LA GRAN FAMILIA</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-15.84749</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.01739</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-15.841331</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-70.02985</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>855753</t>
+          <t>441659</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70025 INDEPENDENCIA NACIONAL</t>
+          <t>SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-15.83136</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.02768</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>-15.883963</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.001613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>444035</t>
+          <t>441640</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MAÑAZO</t>
+          <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-15.800255</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-70.353867</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-15.837603</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-70.027239</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>441367</t>
+          <t>441635</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-15.829512</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.019501</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-15.842175</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.026634</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>441862</t>
+          <t>441621</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADVENTISTA PUNO</t>
+          <t>GLORIOSO SAN CARLOS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-15.83649</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.02933</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>-15.83523</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.023572</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>441348</t>
+          <t>441616</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>71001 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-15.845818</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.01849</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>-15.839062</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-70.023897</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>441386</t>
+          <t>441560</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>POLITECNICO HUASCAR</t>
+          <t>VILLA DEL LAGO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-15.82696</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.03236</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-15.859773</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-70.014508</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>441292</t>
+          <t>441522</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70003 SAGRADO CORAZON DE JESUS</t>
+          <t>70623</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-15.84083</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.021202</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>-15.853321</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-70.017613</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>441560</t>
+          <t>441386</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VILLA DEL LAGO</t>
+          <t>POLITECNICO HUASCAR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-15.859773</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.014508</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-15.82696</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-70.03236</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>441876</t>
+          <t>441367</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-15.840065</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-70.029819</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>-15.829512</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-70.019501</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>907634</t>
+          <t>441348</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JAMES BALDWIN</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-15.845125</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.023615</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-15.845818</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-70.01849</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>577803</t>
+          <t>441310</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>GRAN UNIDAD ESCOLAR SAN CARLOS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-15.836925</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.027213</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>-15.840344</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-70.02443</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>441089</t>
+          <t>441305</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA NACIONAL</t>
+          <t>70005 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-15.831365</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.027684</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>-15.841065</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-70.026032</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>441659</t>
+          <t>441292</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN JUAN BOSCO</t>
+          <t>70003 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-15.883963</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.001613</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-15.84083</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-70.021202</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>441819</t>
+          <t>441287</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-15.841857</t>
+          <t>518</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-70.023737</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>-15.839781</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-70.031459</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>441305</t>
+          <t>441249</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70005 CORAZON DE JESUS</t>
+          <t>326 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-15.841065</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.026032</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>-15.84347</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-70.02109</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>441824</t>
+          <t>441206</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA MERCED</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-15.837837</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.024328</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>-15.883757</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-69.972323</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>441616</t>
+          <t>441089</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>71001 ALMIRANTE MIGUEL GRAU</t>
+          <t>INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-15.839062</t>
+          <t>610</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.023897</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>-15.831365</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-70.027684</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>441621</t>
+          <t>441051</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GLORIOSO SAN CARLOS</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-15.83523</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.023572</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>-15.856057</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-70.012397</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>441683</t>
+          <t>441046</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>45 EMILIO ROMERO PADILLA</t>
+          <t>254 / 70045</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-15.841397</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.025192</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>-15.855837</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-70.007227</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>441678</t>
+          <t>440933</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-15.847185</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.017189</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>-15.838498</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-70.032551</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>441664</t>
+          <t>440928</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>193 CLUB DE LEONES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-15.841331</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.02985</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>-15.84361</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-70.02827</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GLORIOSO SAN CARLOS</t>
+          <t>EL CASTILLO DE LA GRAN FAMILIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-15.837603</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.027239</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>-15.84749</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-70.01739</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
+++ b/ZonasEscolares/excels/PUNO-PUNO-PUNO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
